--- a/GameData/DataTables/Meta/CalibrationTable.xlsx
+++ b/GameData/DataTables/Meta/CalibrationTable.xlsx
@@ -1118,32 +1118,32 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="B22" t="n">
         <v>18</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>REPAIR-SCORE</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>维修效果分</t>
         </is>
-      </c>
-      <c r="E22" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" t="n">
-        <v>20</v>
       </c>
       <c r="G22" t="n">
         <v>20</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>默认维修对象每次有效维修效果分</t>
         </is>
